--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -272,7 +272,7 @@
     <t>内視鏡を使用して実施された検査、治療に関する診断レポート。</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>製品またはシステムが管理する、施設内で診断レポートを一意に識別するためのID。</t>
   </si>
   <si>
-    <t>通常、診断サービスプロバイダの情報システム（フィラーID）によって割り当てられる。</t>
+    <t>通常、診断サービスを実施した施設の情報システム（実施者ID、HL7 v2 の filler ID）によって割り当てられる。</t>
   </si>
   <si>
     <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>
